--- a/topic/excel/煤矿+法规.xlsx
+++ b/topic/excel/煤矿+法规.xlsx
@@ -1390,7 +1390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="11.5666666666667" customWidth="1" style="8" min="1" max="1"/>
@@ -3225,6 +3225,476 @@
         </is>
       </c>
     </row>
+    <row r="45" ht="60" customHeight="1" s="8">
+      <c r="A45" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>根据《煤矿安全规程》第一百五十五条，关于煤仓、溜煤(矸)眼的设计、使用和管理，下列说法正确的是？</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>煤仓可以兼作流水道，以利于排水</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>煤仓上口应当高于巷道底板</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>处置堵仓时，人员可以从下方进入检查</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>放煤硐室可以直接置于煤仓下口处</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>依据规程，煤仓严禁兼作流水道，煤仓上口应当高于巷道底板，处置堵仓时严禁人员从下方进入，放煤硐室严禁直接置于煤仓下口处。</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1" s="8">
+      <c r="A46" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>根据《煤矿安全规程》第七百二十四条，下列哪种情形不得从事井下工作？</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>风湿病（反复活动）</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>轻度感冒</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>轻微皮肤过敏</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>轻度高血压</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>依据该条规定，风湿病（反复活动）属于不得从事井下工作的病症之一。</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1" s="8">
+      <c r="A47" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>根据《煤矿安全规程》第二百五十七条，井口房和通风机房附近多少米内不得有烟火或者用火炉取暖？</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>20m</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>30m</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>规程规定井口房和通风机房附近20m内不得有烟火或用火炉取暖。</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1" s="8">
+      <c r="A48" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>根据规定，立井井筒穿过冲积层、松软岩层或者煤层时，若采用井圈或其他临时支护，临时支护必须符合下列哪项要求？</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>安全可靠、紧靠工作面</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>安全可靠、远离工作面</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>坚固耐用、紧靠井口</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>轻便灵活、紧靠吊盘</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>依据法规原文，采用井圈或其他临时支护时，临时支护必须安全可靠、紧靠工作面。</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1" s="8">
+      <c r="A49" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>根据规定，工作帮边坡在临近最终设计的边坡之前，必须进行什么鉴定？</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>滑坡危险性鉴定</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>边坡稳定性验算</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>地质勘探鉴定</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>安全等级评定</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>依据规定，工作帮边坡在临近最终设计的边坡之前，必须进行滑坡危险性鉴定。</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1" s="8">
+      <c r="A50" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>依据《煤矿安全规程》第一百九十二条，无煤柱开采沿空送巷和沿空留巷时，应当采取与采空区隔离的什么措施？</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>防止漏风措施</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>防止漏水措施</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>防止塌方措施</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>防止瓦斯措施</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>法规原文规定，无煤柱开采沿空送巷和沿空留巷时，应当采取与采空区隔离的防止漏风措施。</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1" s="8">
+      <c r="A51" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>根据《煤矿安全规程》第五百八十三条，在高温区、自然发火区进行爆破作业时，对于有明火的炮孔或孔内温度在80℃以上的高温炮孔，必须采取什么措施？</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>立即装药起爆</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>灭火、降温措施</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>增加炸药用量</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>使用普通炸药</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>依据条文，有明火或80℃以上高温炮孔必须采取灭火、降温措施。</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1" s="8">
+      <c r="A52" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>根据《煤矿安全规程》第二百三十一条，突出煤层采掘工作面经工作面预测后，未进行突出预测的采掘工作面应视为？</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>无突出危险工作面</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>突出危险工作面</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>低瓦斯工作面</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>高瓦斯工作面</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>依据该条规定，未进行突出预测的采掘工作面视为突出危险工作面。</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1" s="8">
+      <c r="A53" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国民法典》第五百七十七条规定，起爆前，必须将所有人员撤至何处？</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>安全地点</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>警戒线外</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>掩体后方</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>指定集合点</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>依据民法典第五百七十七条，起爆前必须将所有人员撤至安全地点。</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1" s="8">
+      <c r="A54" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>根据《煤矿安全规程》第五百九十三条，单斗挖掘机向自移式破碎机装载时，勺斗斗底板下缘距受料斗的距离不得超过多少米？</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>0.5m</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>0.8m</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>1.0m</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>1.5m</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>依据第五百九十三条第一项，卸载时勺斗斗底板下缘距受料斗不得超过0.8m。</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K5"/>
